--- a/artfynd/A 28035-2023 artfynd.xlsx
+++ b/artfynd/A 28035-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 28035-2023 artfynd.xlsx
+++ b/artfynd/A 28035-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AY56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>93752928</v>
+        <v>93752924</v>
       </c>
       <c r="B2" t="n">
-        <v>42705</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503583.4989914641</v>
+        <v>503650</v>
       </c>
       <c r="R2" t="n">
-        <v>6610008.134746497</v>
+        <v>6609996</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -762,19 +757,9 @@
           <t>2020-09-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-09-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -820,15 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>93752927</v>
+        <v>93752925</v>
       </c>
       <c r="B3" t="n">
-        <v>42705</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -874,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503592.6229445575</v>
+        <v>503648</v>
       </c>
       <c r="R3" t="n">
-        <v>6610004.097086812</v>
+        <v>6609985</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -907,19 +887,9 @@
           <t>2020-09-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-09-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -968,12 +938,7 @@
         <v>93752926</v>
       </c>
       <c r="B4" t="n">
-        <v>42705</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503598.7127182387</v>
+        <v>503598</v>
       </c>
       <c r="R4" t="n">
-        <v>6609993.986914258</v>
+        <v>6609994</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1052,19 +1017,9 @@
           <t>2020-09-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-09-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1110,15 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>93752925</v>
+        <v>93752927</v>
       </c>
       <c r="B5" t="n">
-        <v>42705</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1164,10 +1114,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503647.8688252424</v>
+        <v>503592</v>
       </c>
       <c r="R5" t="n">
-        <v>6609984.930024188</v>
+        <v>6610004</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1197,19 +1147,9 @@
           <t>2020-09-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-09-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1255,15 +1195,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>93752924</v>
+        <v>93752928</v>
       </c>
       <c r="B6" t="n">
-        <v>42705</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1309,10 +1244,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503649.3784979182</v>
+        <v>503583</v>
       </c>
       <c r="R6" t="n">
-        <v>6609995.553339321</v>
+        <v>6610008</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1342,19 +1277,9 @@
           <t>2020-09-03</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-09-03</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1403,12 +1328,7 @@
         <v>93752929</v>
       </c>
       <c r="B7" t="n">
-        <v>42705</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1454,10 +1374,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503580.4459132021</v>
+        <v>503580</v>
       </c>
       <c r="R7" t="n">
-        <v>6610021.788393787</v>
+        <v>6610022</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1487,19 +1407,9 @@
           <t>2020-09-03</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-09-03</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1545,15 +1455,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97080302</v>
+        <v>93752930</v>
       </c>
       <c r="B8" t="n">
-        <v>42705</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1588,19 +1493,24 @@
           <t>kolonier</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ömanstorp yta 7:1, Vstm</t>
+          <t>Natorp och Ömanstorpet (Uskavi och Siggeboda) Delyta 7:1, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503640.7749002601</v>
+        <v>503574</v>
       </c>
       <c r="R8" t="n">
-        <v>6609985.428925046</v>
+        <v>6610014</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1624,27 +1534,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Larvstadie 3. Urkrupen.</t>
+          <t>2020-09-03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1693,12 +1588,7 @@
         <v>97080301</v>
       </c>
       <c r="B9" t="n">
-        <v>42705</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1739,10 +1629,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503675.7368774501</v>
+        <v>503676</v>
       </c>
       <c r="R9" t="n">
-        <v>6609983.945662298</v>
+        <v>6609984</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1772,19 +1662,9 @@
           <t>2021-09-14</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-09-14</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1835,15 +1715,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>97080303</v>
+        <v>97080302</v>
       </c>
       <c r="B10" t="n">
-        <v>42705</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1884,10 +1759,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503600.737463653</v>
+        <v>503641</v>
       </c>
       <c r="R10" t="n">
-        <v>6609996.012065982</v>
+        <v>6609986</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1917,24 +1792,14 @@
           <t>2021-09-14</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-09-14</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Larvstadie 3. Urkrupen och delvis nerramlad.</t>
+          <t>Larvstadie 3. Urkrupen.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1980,15 +1845,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>105554824</v>
+        <v>97080303</v>
       </c>
       <c r="B11" t="n">
-        <v>42705</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2025,14 +1885,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Natorpsområdet Yta 7:1 Långbansgruvorna, Vstm</t>
+          <t>Ömanstorp yta 7:1, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503649.8984776841</v>
+        <v>503600</v>
       </c>
       <c r="R11" t="n">
-        <v>6609981.897183133</v>
+        <v>6609996</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2059,27 +1919,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Räkning av larvkolonier (spånader) inom Biogeografisk uppföljning av fjärilar.</t>
+          <t>Larvstadie 3. Urkrupen och delvis nerramlad.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2114,7 +1964,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Inger Holst</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -2125,15 +1975,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>105554827</v>
+        <v>105554822</v>
       </c>
       <c r="B12" t="n">
-        <v>42705</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2160,7 +2005,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2174,10 +2019,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503587.5504190139</v>
+        <v>503674</v>
       </c>
       <c r="R12" t="n">
-        <v>6610010.161822959</v>
+        <v>6609980</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2207,19 +2052,9 @@
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2270,15 +2105,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>105554822</v>
+        <v>105554823</v>
       </c>
       <c r="B13" t="n">
-        <v>42705</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2305,7 +2135,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2319,10 +2149,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>503673.7141503327</v>
+        <v>503684</v>
       </c>
       <c r="R13" t="n">
-        <v>6609979.897251892</v>
+        <v>6609977</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2352,19 +2182,9 @@
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2415,15 +2235,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>105554825</v>
+        <v>105554824</v>
       </c>
       <c r="B14" t="n">
-        <v>42705</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2464,10 +2279,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503641.7911983774</v>
+        <v>503650</v>
       </c>
       <c r="R14" t="n">
-        <v>6609982.395095181</v>
+        <v>6609982</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2497,19 +2312,9 @@
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2560,15 +2365,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>105554823</v>
+        <v>105554825</v>
       </c>
       <c r="B15" t="n">
-        <v>42705</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2609,10 +2409,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503683.8501274239</v>
+        <v>503642</v>
       </c>
       <c r="R15" t="n">
-        <v>6609977.378188322</v>
+        <v>6609983</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2642,19 +2442,9 @@
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2705,15 +2495,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112821011</v>
+        <v>105554827</v>
       </c>
       <c r="B16" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2721,38 +2506,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>kolonier</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>400 m S Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:1 Långbansgruvorna, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>503632</v>
+        <v>503587</v>
       </c>
       <c r="R16" t="n">
-        <v>6609986</v>
+        <v>6610010</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2779,17 +2569,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Från 2 till 4 m höga. Utanför vägkants röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Räkning av larvkolonier (spånader) inom Biogeografisk uppföljning av fjärilar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2800,31 +2590,45 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Inger Holst</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112821021</v>
+        <v>113473040</v>
       </c>
       <c r="B17" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2832,38 +2636,43 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>kolonier</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>400 m S Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:1 Långbansgruvorna, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503651</v>
+        <v>503582</v>
       </c>
       <c r="R17" t="n">
-        <v>6609993</v>
+        <v>6610004</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2890,17 +2699,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Från 0.1 till 2 m höga. Utanför vägkants-röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2911,70 +2715,89 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Inger Holst</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112820988</v>
+        <v>113473565</v>
       </c>
       <c r="B18" t="n">
-        <v>102635</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222412</v>
+        <v>100943</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>kolonier</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>400 m S Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:1 Långbansgruvorna, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503584</v>
+        <v>503653</v>
       </c>
       <c r="R18" t="n">
-        <v>6610029</v>
+        <v>6609996</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3001,12 +2824,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3017,53 +2840,67 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Inger Holst</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112820992</v>
+        <v>113473566</v>
       </c>
       <c r="B19" t="n">
-        <v>102635</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222412</v>
+        <v>100943</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -3071,16 +2908,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>400 m S Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:1 Långbansgruvorna, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503606</v>
+        <v>503623</v>
       </c>
       <c r="R19" t="n">
-        <v>6610046</v>
+        <v>6609987</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3107,12 +2949,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3123,31 +2965,45 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Inger Holst</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112820999</v>
+        <v>113473567</v>
       </c>
       <c r="B20" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3155,38 +3011,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>kolonier</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>400 m S Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:1 Långbansgruvorna, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503634</v>
+        <v>503579</v>
       </c>
       <c r="R20" t="n">
-        <v>6610061</v>
+        <v>6610017</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3213,17 +3074,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Från 0.1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3234,11 +3090,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -3246,19 +3117,18 @@
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112821009</v>
+        <v>120766200</v>
       </c>
       <c r="B21" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3266,38 +3136,48 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>400 m S Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:1 Långbansgruvorna, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503651</v>
+        <v>503620</v>
       </c>
       <c r="R21" t="n">
-        <v>6609980</v>
+        <v>6609995</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3324,17 +3204,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Från 0.3 till 1 m höga. Inom röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Kolonin var belägen 4 m över marken.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3345,11 +3225,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -3357,19 +3252,18 @@
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AY21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112820991</v>
+        <v>120766201</v>
       </c>
       <c r="B22" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3377,38 +3271,48 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>400 m S Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:1 Långbansgruvorna, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503601</v>
+        <v>503574</v>
       </c>
       <c r="R22" t="n">
-        <v>6610045</v>
+        <v>6610012</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3435,17 +3339,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Från 0.1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3456,11 +3355,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
@@ -3468,19 +3382,18 @@
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112821017</v>
+        <v>120766203</v>
       </c>
       <c r="B23" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3488,38 +3401,48 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>400 m S Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:1 Långbansgruvorna, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503605</v>
+        <v>503584</v>
       </c>
       <c r="R23" t="n">
-        <v>6610004</v>
+        <v>6610013</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3546,17 +3469,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Från 0.1 till 2 m höga. Utanför vägkants-röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3567,11 +3485,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
@@ -3579,19 +3512,18 @@
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112820989</v>
+        <v>120766204</v>
       </c>
       <c r="B24" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3599,38 +3531,48 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>400 m S Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:1 Långbansgruvorna, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503587</v>
+        <v>503679</v>
       </c>
       <c r="R24" t="n">
-        <v>6610031</v>
+        <v>6609984</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3657,17 +3599,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Från 0.1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3678,11 +3615,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
@@ -3690,19 +3642,18 @@
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112821022</v>
+        <v>120766205</v>
       </c>
       <c r="B25" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3710,38 +3661,48 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>400 m S Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:1 Långbansgruvorna, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503628</v>
+        <v>503641</v>
       </c>
       <c r="R25" t="n">
-        <v>6610017</v>
+        <v>6609990</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3768,17 +3729,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Från 0.1 till 0.5 m höga. Utanför vägkants röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Kolonin var belägen 4 m över marken.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3789,11 +3750,26 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
@@ -3801,19 +3777,18 @@
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112821014</v>
+        <v>120766206</v>
       </c>
       <c r="B26" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3821,38 +3796,48 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>400 m S Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:1 Långbansgruvorna, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503600</v>
+        <v>503641</v>
       </c>
       <c r="R26" t="n">
-        <v>6609996</v>
+        <v>6609994</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3879,17 +3864,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Från 1 till 5 m höga. Utanför vägkants röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3900,11 +3880,26 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
@@ -3912,19 +3907,18 @@
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112821012</v>
+        <v>129833522</v>
       </c>
       <c r="B27" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3932,38 +3926,48 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>400 m S Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:1 Långbansgruvorna, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503629</v>
+        <v>503588</v>
       </c>
       <c r="R27" t="n">
-        <v>6609985</v>
+        <v>6610011</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3990,17 +3994,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Från 0.1 till 1 m höga. I vägkants röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4011,31 +4010,45 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Inger Holst</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112821020</v>
+        <v>112820989</v>
       </c>
       <c r="B28" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4062,7 +4075,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -4071,10 +4084,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>503640</v>
+        <v>503587</v>
       </c>
       <c r="R28" t="n">
-        <v>6609995</v>
+        <v>6610031</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4111,7 +4124,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Från 0.1 till 3 m höga. Utanför vägkants-röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Från 0.1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4138,15 +4151,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112821018</v>
+        <v>112820991</v>
       </c>
       <c r="B29" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4173,7 +4181,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4182,10 +4190,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503617</v>
+        <v>503601</v>
       </c>
       <c r="R29" t="n">
-        <v>6610004</v>
+        <v>6610045</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4222,7 +4230,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Från 0.1 till 2 m höga. Utanför vägkants-röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Från 0.1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4249,15 +4257,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112821013</v>
+        <v>112820997</v>
       </c>
       <c r="B30" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4293,10 +4296,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503599</v>
+        <v>503611</v>
       </c>
       <c r="R30" t="n">
-        <v>6609994</v>
+        <v>6610058</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4333,7 +4336,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Från 0.1 till 1 m höga. I vägkants röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Från 0.1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4360,15 +4363,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112821019</v>
+        <v>112820998</v>
       </c>
       <c r="B31" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4395,7 +4393,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4404,10 +4402,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503626</v>
+        <v>503623</v>
       </c>
       <c r="R31" t="n">
-        <v>6609997</v>
+        <v>6610071</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4444,7 +4442,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Från 0.1 till 2 m höga. Utanför vägkants-röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Från 0.1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4471,15 +4469,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112821010</v>
+        <v>112820999</v>
       </c>
       <c r="B32" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4506,7 +4499,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4515,10 +4508,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503647</v>
+        <v>503634</v>
       </c>
       <c r="R32" t="n">
-        <v>6609981</v>
+        <v>6610062</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4555,7 +4548,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Från 2 till 4 m höga. Utanför vägkants röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Från 0.1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4582,15 +4575,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113473566</v>
+        <v>112821000</v>
       </c>
       <c r="B33" t="n">
-        <v>42896</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4598,43 +4586,38 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100943</v>
+        <v>220785</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Asknätfjäril</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Euphydryas maturna</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>kolonier</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Natorpsområdet Yta 7:1 Långbansgruvorna, Vstm</t>
+          <t>400 m S Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503623</v>
+        <v>503720</v>
       </c>
       <c r="R33" t="n">
-        <v>6609987</v>
+        <v>6610045</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4661,12 +4644,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Från 0.1 till 1 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4677,50 +4665,26 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Inger Holst</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av fjärilar</t>
-        </is>
-      </c>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113473040</v>
+        <v>112821001</v>
       </c>
       <c r="B34" t="n">
-        <v>42896</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4728,43 +4692,38 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100943</v>
+        <v>220785</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Asknätfjäril</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Euphydryas maturna</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>kolonier</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Natorpsområdet Yta 7:1 Långbansgruvorna, Vstm</t>
+          <t>400 m S Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503582</v>
+        <v>503710</v>
       </c>
       <c r="R34" t="n">
-        <v>6610004</v>
+        <v>6610087</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4791,12 +4750,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ca 1 m hög. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4807,50 +4771,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Inger Holst</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av fjärilar</t>
-        </is>
-      </c>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113473565</v>
+        <v>112821004</v>
       </c>
       <c r="B35" t="n">
-        <v>42896</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4858,43 +4798,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100943</v>
+        <v>220785</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Asknätfjäril</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Euphydryas maturna</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>kolonier</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Natorpsområdet Yta 7:1 Långbansgruvorna, Vstm</t>
+          <t>400 m S Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503653</v>
+        <v>503715</v>
       </c>
       <c r="R35" t="n">
-        <v>6609996</v>
+        <v>6610027</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4921,12 +4856,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Från 0.5 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4937,50 +4877,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Inger Holst</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av fjärilar</t>
-        </is>
-      </c>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120766205</v>
+        <v>112821007</v>
       </c>
       <c r="B36" t="n">
-        <v>42961</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4988,48 +4904,38 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100943</v>
+        <v>220785</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Asknätfjäril</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Euphydryas maturna</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>kolonier</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Natorpsområdet Yta 7:1 Långbansgruvorna, Vstm</t>
+          <t>400 m S Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503641</v>
+        <v>503720</v>
       </c>
       <c r="R36" t="n">
-        <v>6609990</v>
+        <v>6610009</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5056,17 +4962,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Kolonin var belägen 4 m över marken.</t>
+          <t>Från 0.5 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5077,26 +4983,11 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
@@ -5104,23 +4995,14 @@
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av fjärilar</t>
-        </is>
-      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120766204</v>
+        <v>112821009</v>
       </c>
       <c r="B37" t="n">
-        <v>42961</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5128,48 +5010,38 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100943</v>
+        <v>220785</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Asknätfjäril</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Euphydryas maturna</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>kolonier</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Natorpsområdet Yta 7:1 Långbansgruvorna, Vstm</t>
+          <t>400 m S Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503679</v>
+        <v>503651</v>
       </c>
       <c r="R37" t="n">
-        <v>6609984</v>
+        <v>6609980</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5196,12 +5068,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Från 0.3 till 1 m höga. Inom röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5212,26 +5089,11 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
@@ -5239,23 +5101,14 @@
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av fjärilar</t>
-        </is>
-      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120766203</v>
+        <v>112821010</v>
       </c>
       <c r="B38" t="n">
-        <v>42961</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5263,48 +5116,38 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100943</v>
+        <v>220785</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Asknätfjäril</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Euphydryas maturna</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>kolonier</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Natorpsområdet Yta 7:1 Långbansgruvorna, Vstm</t>
+          <t>400 m S Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>503584</v>
+        <v>503647</v>
       </c>
       <c r="R38" t="n">
-        <v>6610013</v>
+        <v>6609981</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5331,12 +5174,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Från 2 till 4 m höga. Utanför vägkants röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5347,26 +5195,11 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
@@ -5374,23 +5207,14 @@
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av fjärilar</t>
-        </is>
-      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120766206</v>
+        <v>112821011</v>
       </c>
       <c r="B39" t="n">
-        <v>42961</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5398,48 +5222,38 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100943</v>
+        <v>220785</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Asknätfjäril</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Euphydryas maturna</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>kolonier</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Natorpsområdet Yta 7:1 Långbansgruvorna, Vstm</t>
+          <t>400 m S Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>503641</v>
+        <v>503632</v>
       </c>
       <c r="R39" t="n">
-        <v>6609994</v>
+        <v>6609987</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5466,12 +5280,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Från 2 till 4 m höga. Utanför vägkants röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5482,26 +5301,11 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
@@ -5509,23 +5313,14 @@
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av fjärilar</t>
-        </is>
-      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120766200</v>
+        <v>112821012</v>
       </c>
       <c r="B40" t="n">
-        <v>42961</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5533,48 +5328,38 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100943</v>
+        <v>220785</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Asknätfjäril</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Euphydryas maturna</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>kolonier</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Natorpsområdet Yta 7:1 Långbansgruvorna, Vstm</t>
+          <t>400 m S Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>503620</v>
+        <v>503629</v>
       </c>
       <c r="R40" t="n">
-        <v>6609995</v>
+        <v>6609986</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5601,17 +5386,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Kolonin var belägen 4 m över marken.</t>
+          <t>Från 0.1 till 1 m höga. I vägkants röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5622,26 +5407,11 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
@@ -5649,11 +5419,1670 @@
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AY40" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av fjärilar</t>
-        </is>
-      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>112821013</v>
+      </c>
+      <c r="B41" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>400 m S Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>503598</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6609994</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Från 0.1 till 1 m höga. I vägkants röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>112821014</v>
+      </c>
+      <c r="B42" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>400 m S Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>503599</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6609996</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Från 1 till 5 m höga. Utanför vägkants röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>112821015</v>
+      </c>
+      <c r="B43" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>400 m S Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>503578</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6610010</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Från 0.1 till 2 m höga. Utanför vägkants-röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>112821017</v>
+      </c>
+      <c r="B44" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>400 m S Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>503606</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6610004</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Från 0.1 till 2 m höga. Utanför vägkants-röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>112821018</v>
+      </c>
+      <c r="B45" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>400 m S Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>503618</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6610004</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Från 0.1 till 2 m höga. Utanför vägkants-röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>112821019</v>
+      </c>
+      <c r="B46" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>400 m S Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>503626</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6609996</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Från 0.1 till 2 m höga. Utanför vägkants-röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>112821020</v>
+      </c>
+      <c r="B47" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>400 m S Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>503639</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6609995</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Från 0.1 till 3 m höga. Utanför vägkants-röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>112821021</v>
+      </c>
+      <c r="B48" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>400 m S Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>503652</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6609993</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Från 0.1 till 2 m höga. Utanför vägkants-röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>112821022</v>
+      </c>
+      <c r="B49" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>400 m S Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>503627</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6610018</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Från 0.1 till 0.5 m höga. Utanför vägkants röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>112821023</v>
+      </c>
+      <c r="B50" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>400 m S Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>503568</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6610017</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Från 0.1 till 2 m höga. Utanför vägkants-röjzonen. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>112821025</v>
+      </c>
+      <c r="B51" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>400 m S Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>503572</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6610007</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Från 0.5 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>112821024</v>
+      </c>
+      <c r="B52" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>400 m S Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>503576</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6610009</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>112820988</v>
+      </c>
+      <c r="B53" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>400 m S Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>503584</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6610029</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>112820992</v>
+      </c>
+      <c r="B54" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>400 m S Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>503606</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6610046</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>112820996</v>
+      </c>
+      <c r="B55" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>400 m S Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>503611</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6610061</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>112820993</v>
+      </c>
+      <c r="B56" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>400 m S Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>503612</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6610054</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28035-2023 artfynd.xlsx
+++ b/artfynd/A 28035-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY56"/>
+  <dimension ref="A1:AZ56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -802,6 +807,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93752924</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -932,6 +942,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93752925</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1062,6 +1077,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93752926</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1192,6 +1212,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93752927</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1322,6 +1347,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93752928</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1452,6 +1482,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93752929</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1582,6 +1617,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93752930</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1712,6 +1752,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97080301</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1842,6 +1887,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97080302</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1972,6 +2022,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97080303</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2102,6 +2157,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105554822</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2232,6 +2292,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105554823</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2362,6 +2427,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105554824</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2492,6 +2562,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105554825</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2622,6 +2697,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105554827</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2747,6 +2827,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113473040</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2872,6 +2957,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113473565</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2997,6 +3087,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113473566</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3122,6 +3217,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113473567</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3257,6 +3357,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120766200</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3387,6 +3492,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120766201</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3517,6 +3627,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120766203</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3647,6 +3762,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120766204</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3782,6 +3902,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120766205</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3912,6 +4037,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120766206</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4042,6 +4172,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129833522</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4148,6 +4283,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820989</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4254,6 +4394,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820991</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4360,6 +4505,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820997</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4466,6 +4616,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820998</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4572,6 +4727,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820999</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4678,6 +4838,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112821000</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4784,6 +4949,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112821001</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4890,6 +5060,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112821004</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4996,6 +5171,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112821007</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5102,6 +5282,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112821009</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5208,6 +5393,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112821010</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5314,6 +5504,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112821011</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5420,6 +5615,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112821012</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5526,6 +5726,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112821013</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5632,6 +5837,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112821014</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5738,6 +5948,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112821015</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5844,6 +6059,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112821017</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5950,6 +6170,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112821018</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6056,6 +6281,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112821019</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6162,6 +6392,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112821020</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6268,6 +6503,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112821021</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6374,6 +6614,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112821022</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6480,6 +6725,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112821023</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6586,6 +6836,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112821025</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6683,6 +6938,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112821024</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6784,6 +7044,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820988</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6885,6 +7150,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820992</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6986,6 +7256,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820996</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7083,8 +7358,70 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820993</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>